--- a/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleError.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleError.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="97">
   <si>
     <r>
       <rPr>
@@ -126,6 +126,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFF54A45"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -274,25 +281,145 @@
     </r>
   </si>
   <si>
-    <t>物流时效（海运）</t>
-  </si>
-  <si>
-    <t>发货频率（海运)</t>
-  </si>
-  <si>
-    <t>优先级（海运)</t>
-  </si>
-  <si>
-    <t>物流时效（***）</t>
-  </si>
-  <si>
-    <t>发货频率（***）</t>
-  </si>
-  <si>
-    <t>优先级（***）</t>
-  </si>
-  <si>
-    <t>序号</t>
+    <t>物流时效（空运）</t>
+  </si>
+  <si>
+    <t>发货频率（空运)</t>
+  </si>
+  <si>
+    <t>优先级（空运)</t>
+  </si>
+  <si>
+    <t>物流时效（快递）</t>
+  </si>
+  <si>
+    <t>发货频率（快递）</t>
+  </si>
+  <si>
+    <t>优先级（快递）</t>
+  </si>
+  <si>
+    <t>物流时效（海运散装）</t>
+  </si>
+  <si>
+    <t>发货频率（海运散装）</t>
+  </si>
+  <si>
+    <t>优先级（海运散装)</t>
+  </si>
+  <si>
+    <t>物流时效（海运整柜）</t>
+  </si>
+  <si>
+    <t>发货频率（海运整柜）</t>
+  </si>
+  <si>
+    <t>优先级（海运整柜)</t>
+  </si>
+  <si>
+    <t>物流时效（铁运散装）</t>
+  </si>
+  <si>
+    <t>发货频率（铁运散装）</t>
+  </si>
+  <si>
+    <t>优先级（铁运散装)</t>
+  </si>
+  <si>
+    <t>物流时效（铁运整柜）</t>
+  </si>
+  <si>
+    <t>发货频率（铁运整柜）</t>
+  </si>
+  <si>
+    <t>优先级（铁运整柜)</t>
+  </si>
+  <si>
+    <t>{.platform}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.shopName}</t>
+  </si>
+  <si>
+    <t>{.purchaseApproveDays}</t>
+  </si>
+  <si>
+    <t>{.productionDays}</t>
+  </si>
+  <si>
+    <t>{.supplierDeliveryDays}</t>
+  </si>
+  <si>
+    <t>{.qcDays}</t>
+  </si>
+  <si>
+    <t>{.purchaseCycleDays}</t>
+  </si>
+  <si>
+    <t>{.oneLogisticsDays}</t>
+  </si>
+  <si>
+    <t>{.oneLogisticsCycleDays}</t>
+  </si>
+  <si>
+    <t>{.oneIndex}</t>
+  </si>
+  <si>
+    <t>{.twoLogisticsDays}</t>
+  </si>
+  <si>
+    <t>{.twoLogisticsCycleDays}</t>
+  </si>
+  <si>
+    <t>{.twoIndex}</t>
+  </si>
+  <si>
+    <t>{.threeLogisticsDays}</t>
+  </si>
+  <si>
+    <t>{.threeLogisticsCycleDays}</t>
+  </si>
+  <si>
+    <t>{.threeIndex}</t>
+  </si>
+  <si>
+    <t>{.fourLogisticsDays}</t>
+  </si>
+  <si>
+    <t>{.fourLogisticsCycleDays}</t>
+  </si>
+  <si>
+    <t>{.fourIndex}</t>
+  </si>
+  <si>
+    <t>{.fiveLogisticsDays}</t>
+  </si>
+  <si>
+    <t>{.fiveLogisticsCycleDays}</t>
+  </si>
+  <si>
+    <t>{.fiveIndex}</t>
+  </si>
+  <si>
+    <t>{.sixLogisticsDays}</t>
+  </si>
+  <si>
+    <t>{.sixLogisticsCycleDays}</t>
+  </si>
+  <si>
+    <t>{.sixIndex}</t>
+  </si>
+  <si>
+    <t>{.safeDays}</t>
+  </si>
+  <si>
+    <t>{.stockingRatio}</t>
+  </si>
+  <si>
+    <t>{.errorMsg}</t>
   </si>
   <si>
     <r>
@@ -381,6 +508,15 @@
     </r>
   </si>
   <si>
+    <t>{.name}</t>
+  </si>
+  <si>
+    <t>{.startDate}</t>
+  </si>
+  <si>
+    <t>{.endDate}</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -436,6 +572,39 @@
     <t>360天日均（%）</t>
   </si>
   <si>
+    <t>{.defaultTypeName}</t>
+  </si>
+  <si>
+    <t>{.fixedValue}</t>
+  </si>
+  <si>
+    <t>{.threeDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.sevenDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.fourteenDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.thirtyDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.sixtyDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.ninetyDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.oneHundredEightyDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.twoHundredSeventyDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.threeHundredSixtyDaysRatio}</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -498,17 +667,20 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>店铺/渠道</t>
-    </r>
-  </si>
-  <si>
-    <t>*去噪类型</t>
+      <t>去噪类型</t>
+    </r>
   </si>
   <si>
     <t>百分比去噪（%）</t>
   </si>
   <si>
     <t>固定值去噪</t>
+  </si>
+  <si>
+    <t>{.denoisingTypeName}</t>
+  </si>
+  <si>
+    <t>{.percentageValue}</t>
   </si>
 </sst>
 </file>
@@ -538,14 +710,14 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FFF54A45"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFF54A45"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -914,7 +1086,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -966,16 +1138,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -990,6 +1177,96 @@
       </top>
       <bottom style="medium">
         <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1117,7 +1394,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1129,34 +1406,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1241,7 +1518,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1254,44 +1531,77 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1604,10 +1914,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:AC3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
-    <col min="4" max="4" width="13.125" customWidth="1"/>
+    <col min="1" max="1" width="15.75" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="13.25" customWidth="1"/>
     <col min="5" max="5" width="16.125" customWidth="1"/>
     <col min="6" max="6" width="14.5" customWidth="1"/>
     <col min="7" max="7" width="14.625" customWidth="1"/>
@@ -1616,96 +1929,227 @@
     <col min="10" max="10" width="14.375" customWidth="1"/>
     <col min="11" max="11" width="13.875" customWidth="1"/>
     <col min="12" max="12" width="15.125" customWidth="1"/>
-    <col min="13" max="13" width="12.75" customWidth="1"/>
-    <col min="14" max="14" width="11.375" customWidth="1"/>
-    <col min="15" max="15" width="13.625" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="18" max="18" width="12" customWidth="1"/>
+    <col min="13" max="13" width="15.25" customWidth="1"/>
+    <col min="14" max="15" width="13.625" customWidth="1"/>
+    <col min="16" max="16" width="17.875" customWidth="1"/>
+    <col min="17" max="25" width="17.375" customWidth="1"/>
+    <col min="26" max="26" width="16" customWidth="1"/>
+    <col min="27" max="27" width="12.625" customWidth="1"/>
+    <col min="28" max="28" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A1" s="14" t="s">
+    <row r="1" ht="15" customHeight="1" spans="1:29">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="8" t="s">
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="16" t="s">
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="AB1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="AC1" s="24" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="14" t="s">
+    <row r="2" spans="1:29">
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
+      <c r="O2" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="X2" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA2" s="25"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="27"/>
+    </row>
+    <row r="3" spans="1:29">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S3" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" t="s">
+        <v>50</v>
+      </c>
+      <c r="U3" t="s">
+        <v>51</v>
+      </c>
+      <c r="V3" t="s">
+        <v>52</v>
+      </c>
+      <c r="W3" t="s">
+        <v>53</v>
+      </c>
+      <c r="X3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1714,9 +2158,9 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="AA1:AA2"/>
+    <mergeCell ref="AB1:AB2"/>
+    <mergeCell ref="AC1:AC2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1727,18 +2171,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="3" width="11.75" customWidth="1"/>
-    <col min="4" max="4" width="11.25" customWidth="1"/>
-    <col min="5" max="5" width="11.75" customWidth="1"/>
-    <col min="6" max="6" width="11.875" customWidth="1"/>
-    <col min="7" max="8" width="12.5" customWidth="1"/>
+    <col min="2" max="4" width="11.75" customWidth="1"/>
+    <col min="5" max="5" width="14.375" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="7" max="7" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:9">
+    <row r="1" ht="14.25" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1748,23 +2191,46 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>22</v>
+      <c r="D1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="1" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1777,10 +2243,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
-    <col min="4" max="5" width="13.625" customWidth="1"/>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="3" max="3" width="13.75" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="13.625" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="13.125" customWidth="1"/>
@@ -1803,13 +2273,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
@@ -1818,53 +2288,100 @@
       <c r="K1" s="12"/>
       <c r="L1" s="12"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="8" t="s">
+      <c r="N1" s="14"/>
+      <c r="O1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="4"/>
+      <c r="P1" s="10"/>
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
     </row>
     <row r="2" ht="14.25" spans="1:19">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="11"/>
       <c r="F2" s="13" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="10"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L3" t="s">
+        <v>87</v>
+      </c>
+      <c r="M3" t="s">
+        <v>88</v>
+      </c>
+      <c r="N3" t="s">
+        <v>89</v>
+      </c>
+      <c r="O3" t="s">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1885,21 +2402,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:T3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
-    <col min="8" max="8" width="14.375" customWidth="1"/>
-    <col min="9" max="9" width="12.75" customWidth="1"/>
-    <col min="10" max="10" width="13.75" customWidth="1"/>
-    <col min="11" max="11" width="14.125" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="14.125" customWidth="1"/>
-    <col min="14" max="14" width="14.5" customWidth="1"/>
-    <col min="15" max="15" width="14.625" customWidth="1"/>
-    <col min="16" max="16" width="17.25" customWidth="1"/>
+    <col min="1" max="1" width="13.375" customWidth="1"/>
+    <col min="2" max="2" width="15.25" customWidth="1"/>
+    <col min="3" max="3" width="14.125" customWidth="1"/>
+    <col min="4" max="4" width="17.125" customWidth="1"/>
+    <col min="5" max="5" width="17.625" customWidth="1"/>
+    <col min="6" max="6" width="14.875" customWidth="1"/>
+    <col min="7" max="7" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="9" max="10" width="19.375" customWidth="1"/>
+    <col min="11" max="11" width="17.75" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="19.25" customWidth="1"/>
+    <col min="14" max="14" width="14.625" customWidth="1"/>
+    <col min="15" max="15" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:21">
+    <row r="1" ht="15" customHeight="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1909,89 +2431,134 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="8" t="s">
+      <c r="D1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="9"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="4"/>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
     </row>
-    <row r="2" ht="14.25" spans="1:21">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+    <row r="2" ht="14.25" spans="1:20">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="H2" s="5" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>35</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="P2" s="9"/>
       <c r="Q2" s="10"/>
-      <c r="R2" s="9"/>
+      <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" t="s">
+        <v>85</v>
+      </c>
+      <c r="L3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N3" t="s">
+        <v>88</v>
+      </c>
+      <c r="O3" t="s">
+        <v>89</v>
+      </c>
+      <c r="P3" t="s">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="H1:P1"/>
+  <mergeCells count="8">
+    <mergeCell ref="G1:O1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="P1:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2001,16 +2568,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="5" max="5" width="11.375" customWidth="1"/>
-    <col min="6" max="6" width="12.125" customWidth="1"/>
-    <col min="7" max="7" width="11.75" customWidth="1"/>
-    <col min="8" max="8" width="12.875" customWidth="1"/>
+    <col min="1" max="1" width="13.25" customWidth="1"/>
+    <col min="2" max="2" width="15.5" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="12.75" customWidth="1"/>
+    <col min="5" max="5" width="15.875" customWidth="1"/>
+    <col min="6" max="6" width="16.5" customWidth="1"/>
+    <col min="7" max="7" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:21">
+    <row r="1" ht="14.25" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2020,24 +2590,22 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>22</v>
+      <c r="D1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="4"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -2049,7 +2617,32 @@
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" t="s">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2060,21 +2653,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="12.25" customWidth="1"/>
-    <col min="2" max="2" width="10.875" customWidth="1"/>
-    <col min="3" max="3" width="13.875" customWidth="1"/>
-    <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="5" max="5" width="12.625" customWidth="1"/>
-    <col min="6" max="6" width="14.75" customWidth="1"/>
-    <col min="7" max="8" width="13.125" customWidth="1"/>
-    <col min="9" max="9" width="15.125" customWidth="1"/>
-    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="1" max="1" width="14.75" customWidth="1"/>
+    <col min="2" max="2" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="15.375" customWidth="1"/>
+    <col min="4" max="4" width="12.625" customWidth="1"/>
+    <col min="5" max="5" width="14.75" customWidth="1"/>
+    <col min="6" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="15.125" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="14.25" spans="1:23">
+    <row r="1" customFormat="1" ht="14.25" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2082,32 +2674,30 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
@@ -2119,7 +2709,38 @@
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
       <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" t="s">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleError.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleError.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="备货" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="98">
   <si>
     <r>
       <rPr>
@@ -511,10 +511,13 @@
     <t>{.name}</t>
   </si>
   <si>
-    <t>{.startDate}</t>
-  </si>
-  <si>
-    <t>{.endDate}</t>
+    <t>{.startDateStr}</t>
+  </si>
+  <si>
+    <t>{.endDateStr}</t>
+  </si>
+  <si>
+    <t>{.stockingRatioStr}</t>
   </si>
   <si>
     <r>
@@ -1985,7 +1988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" ht="14.25" spans="1:29">
       <c r="A2" s="19"/>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -2227,7 +2230,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H2" t="s">
         <v>59</v>
@@ -2273,13 +2276,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
@@ -2304,31 +2307,31 @@
       <c r="D2" s="3"/>
       <c r="E2" s="11"/>
       <c r="F2" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
@@ -2347,37 +2350,37 @@
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O3" t="s">
         <v>59</v>
@@ -2441,7 +2444,7 @@
         <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -2467,31 +2470,31 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P2" s="9"/>
       <c r="Q2" s="10"/>
@@ -2519,31 +2522,31 @@
         <v>66</v>
       </c>
       <c r="G3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P3" t="s">
         <v>59</v>
@@ -2600,7 +2603,7 @@
         <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
@@ -2638,7 +2641,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s">
         <v>59</v>
@@ -2686,13 +2689,13 @@
         <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>7</v>
@@ -2730,13 +2733,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J2" t="s">
         <v>59</v>

--- a/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleError.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleError.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="备货" sheetId="1" r:id="rId1"/>
@@ -125,160 +125,28 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFF54A45"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>安全天数</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>默认备货系数</t>
-    </r>
+    <t>安全天数</t>
+  </si>
+  <si>
+    <t>默认备货系数</t>
   </si>
   <si>
     <t>错误说明</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>采购审批（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>生产周期（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>供应商发货（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>质检入库（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>采购频率（天）</t>
-    </r>
+    <t>采购审批（天）</t>
+  </si>
+  <si>
+    <t>生产周期（天）</t>
+  </si>
+  <si>
+    <t>供应商发货（天）</t>
+  </si>
+  <si>
+    <t>质检入库（天）</t>
+  </si>
+  <si>
+    <t>采购频率（天）</t>
   </si>
   <si>
     <t>物流时效（空运）</t>
@@ -728,6 +596,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -876,12 +750,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -1391,133 +1259,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1585,13 +1453,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1958,7 +1826,7 @@
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
       <c r="H1" s="18"/>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="21" t="s">
         <v>4</v>
       </c>
       <c r="J1" s="18"/>
@@ -1968,43 +1836,43 @@
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
       <c r="P1" s="18"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-      <c r="Z1" s="23"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
       <c r="AA1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="22" t="s">
+      <c r="AB1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="AC1" s="24" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="14.25" spans="1:29">
+    <row r="2" spans="1:29">
       <c r="A2" s="19"/>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="20" t="s">

--- a/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleError.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleError.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="备货" sheetId="1" r:id="rId1"/>
+    <sheet name="时效 &amp; 备货" sheetId="1" r:id="rId1"/>
     <sheet name="动态备货系数" sheetId="2" r:id="rId2"/>
     <sheet name="默认日销量" sheetId="3" r:id="rId3"/>
     <sheet name="动态日销量" sheetId="4" r:id="rId4"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="99">
   <si>
     <r>
       <rPr>
@@ -125,82 +125,85 @@
     </r>
   </si>
   <si>
+    <t>备货</t>
+  </si>
+  <si>
+    <t>错误说明</t>
+  </si>
+  <si>
+    <t>采购审批（天）</t>
+  </si>
+  <si>
+    <t>生产周期（天）</t>
+  </si>
+  <si>
+    <t>供应商发货（天）</t>
+  </si>
+  <si>
+    <t>质检入库（天）</t>
+  </si>
+  <si>
+    <t>采购频率（天）</t>
+  </si>
+  <si>
+    <t>物流时效（空运）</t>
+  </si>
+  <si>
+    <t>发货频率（空运)</t>
+  </si>
+  <si>
+    <t>优先级（空运)</t>
+  </si>
+  <si>
+    <t>物流时效（快递）</t>
+  </si>
+  <si>
+    <t>发货频率（快递）</t>
+  </si>
+  <si>
+    <t>优先级（快递）</t>
+  </si>
+  <si>
+    <t>物流时效（海运散装）</t>
+  </si>
+  <si>
+    <t>发货频率（海运散装）</t>
+  </si>
+  <si>
+    <t>优先级（海运散装)</t>
+  </si>
+  <si>
+    <t>物流时效（海运整柜）</t>
+  </si>
+  <si>
+    <t>发货频率（海运整柜）</t>
+  </si>
+  <si>
+    <t>优先级（海运整柜)</t>
+  </si>
+  <si>
+    <t>物流时效（铁运散装）</t>
+  </si>
+  <si>
+    <t>发货频率（铁运散装）</t>
+  </si>
+  <si>
+    <t>优先级（铁运散装)</t>
+  </si>
+  <si>
+    <t>物流时效（铁运整柜）</t>
+  </si>
+  <si>
+    <t>发货频率（铁运整柜）</t>
+  </si>
+  <si>
+    <t>优先级（铁运整柜)</t>
+  </si>
+  <si>
     <t>安全天数</t>
   </si>
   <si>
     <t>默认备货系数</t>
-  </si>
-  <si>
-    <t>错误说明</t>
-  </si>
-  <si>
-    <t>采购审批（天）</t>
-  </si>
-  <si>
-    <t>生产周期（天）</t>
-  </si>
-  <si>
-    <t>供应商发货（天）</t>
-  </si>
-  <si>
-    <t>质检入库（天）</t>
-  </si>
-  <si>
-    <t>采购频率（天）</t>
-  </si>
-  <si>
-    <t>物流时效（空运）</t>
-  </si>
-  <si>
-    <t>发货频率（空运)</t>
-  </si>
-  <si>
-    <t>优先级（空运)</t>
-  </si>
-  <si>
-    <t>物流时效（快递）</t>
-  </si>
-  <si>
-    <t>发货频率（快递）</t>
-  </si>
-  <si>
-    <t>优先级（快递）</t>
-  </si>
-  <si>
-    <t>物流时效（海运散装）</t>
-  </si>
-  <si>
-    <t>发货频率（海运散装）</t>
-  </si>
-  <si>
-    <t>优先级（海运散装)</t>
-  </si>
-  <si>
-    <t>物流时效（海运整柜）</t>
-  </si>
-  <si>
-    <t>发货频率（海运整柜）</t>
-  </si>
-  <si>
-    <t>优先级（海运整柜)</t>
-  </si>
-  <si>
-    <t>物流时效（铁运散装）</t>
-  </si>
-  <si>
-    <t>发货频率（铁运散装）</t>
-  </si>
-  <si>
-    <t>优先级（铁运散装)</t>
-  </si>
-  <si>
-    <t>物流时效（铁运整柜）</t>
-  </si>
-  <si>
-    <t>发货频率（铁运整柜）</t>
-  </si>
-  <si>
-    <t>优先级（铁运整柜)</t>
   </si>
   <si>
     <t>{.platform}</t>
@@ -957,7 +960,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1107,6 +1110,32 @@
         <color auto="1"/>
       </top>
       <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1265,7 +1294,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1277,34 +1306,34 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1389,7 +1418,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1459,19 +1488,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1849,188 +1881,189 @@
       <c r="AA1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="18" t="s">
+      <c r="AB1" s="24"/>
+      <c r="AC1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="AC1" s="24" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" ht="14.25" spans="1:29">
       <c r="A2" s="19"/>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
       <c r="D2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="G2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="H2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="I2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="J2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="K2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="L2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="M2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="N2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="O2" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="P2" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="Q2" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="R2" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="S2" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="S2" s="20" t="s">
+      <c r="T2" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="T2" s="20" t="s">
+      <c r="U2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="U2" s="20" t="s">
+      <c r="V2" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="20" t="s">
+      <c r="W2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="20" t="s">
+      <c r="X2" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="X2" s="20" t="s">
+      <c r="Y2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="Y2" s="20" t="s">
+      <c r="Z2" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="Z2" s="20" t="s">
+      <c r="AA2" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="26"/>
-      <c r="AC2" s="27"/>
+      <c r="AB2" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC2" s="28"/>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="V3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="W3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="X3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Z3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AB3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AC3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="I1:P1"/>
+    <mergeCell ref="AA1:AB1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="AB1:AB2"/>
     <mergeCell ref="AC1:AC2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2063,45 +2096,45 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2144,13 +2177,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
@@ -2161,7 +2194,7 @@
       <c r="M1" s="12"/>
       <c r="N1" s="14"/>
       <c r="O1" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P1" s="10"/>
       <c r="Q1" s="4"/>
@@ -2175,31 +2208,31 @@
       <c r="D2" s="3"/>
       <c r="E2" s="11"/>
       <c r="F2" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
@@ -2209,49 +2242,49 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2303,16 +2336,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -2323,7 +2356,7 @@
       <c r="N1" s="3"/>
       <c r="O1" s="6"/>
       <c r="P1" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q1" s="10"/>
       <c r="R1" s="4"/>
@@ -2338,31 +2371,31 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P2" s="9"/>
       <c r="Q2" s="10"/>
@@ -2372,52 +2405,52 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2462,19 +2495,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
@@ -2491,28 +2524,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2548,25 +2581,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -2583,34 +2616,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
